--- a/beispiele/gross/datenraum/2.5 Management Accounts 2025.xlsx
+++ b/beispiele/gross/datenraum/2.5 Management Accounts 2025.xlsx
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>31862</v>
+        <v>32317</v>
       </c>
     </row>
     <row r="3">
